--- a/STOK DEALER/STOCK HARAPAN.xlsx
+++ b/STOK DEALER/STOCK HARAPAN.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC64EB9-830D-49B6-8863-01F0D9361C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7CD17A-AA54-4E3A-865C-20BC76E763F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="STOCK" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -16512,13 +16512,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16824,13 +16824,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17526,13 +17526,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17682,13 +17682,13 @@
         <v>148</v>
       </c>
       <c r="F81" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -17734,13 +17734,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17864,13 +17864,13 @@
         <v>148</v>
       </c>
       <c r="F88" s="2">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="G88" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -18176,13 +18176,13 @@
         <v>98</v>
       </c>
       <c r="F100" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G100" s="2">
         <v>2</v>
       </c>
       <c r="H100" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18202,13 +18202,13 @@
         <v>148</v>
       </c>
       <c r="F101" s="2">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="G101" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2">
-        <v>670</v>
+        <v>658</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -18254,13 +18254,13 @@
         <v>39</v>
       </c>
       <c r="F103" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G103" s="2">
         <v>0</v>
       </c>
       <c r="H103" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18384,13 +18384,13 @@
         <v>148</v>
       </c>
       <c r="F108" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="2">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -22280,10 +22280,10 @@
         <v>363</v>
       </c>
       <c r="F258" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G258" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H258" s="2">
         <v>6</v>
@@ -28934,13 +28934,13 @@
         <v>874</v>
       </c>
       <c r="F514" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G514" s="2">
         <v>0</v>
       </c>
       <c r="H514" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
@@ -33194,13 +33194,13 @@
         <v>854</v>
       </c>
       <c r="F678" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G678" s="2">
         <v>0</v>
       </c>
       <c r="H678" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
@@ -35092,13 +35092,13 @@
         <v>428</v>
       </c>
       <c r="F751" s="2">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G751" s="2">
         <v>0</v>
       </c>
       <c r="H751" s="2">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
@@ -35196,13 +35196,13 @@
         <v>428</v>
       </c>
       <c r="F755" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G755" s="2">
         <v>0</v>
       </c>
       <c r="H755" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
@@ -35508,13 +35508,13 @@
         <v>428</v>
       </c>
       <c r="F767" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G767" s="2">
         <v>0</v>
       </c>
       <c r="H767" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.25">
@@ -39486,10 +39486,10 @@
         <v>1536</v>
       </c>
       <c r="F920" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G920" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H920" s="2">
         <v>5</v>
@@ -39928,13 +39928,13 @@
         <v>1556</v>
       </c>
       <c r="F937" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G937" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H937" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
@@ -49310,13 +49310,13 @@
         <v>98</v>
       </c>
       <c r="F1298" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1298" s="2">
         <v>0</v>
       </c>
       <c r="H1298" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1299" spans="1:8" x14ac:dyDescent="0.25">
@@ -51364,13 +51364,13 @@
         <v>2246</v>
       </c>
       <c r="F1377" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1377" s="2">
         <v>0</v>
       </c>
       <c r="H1377" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
@@ -63480,13 +63480,13 @@
         <v>3145</v>
       </c>
       <c r="F1843" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1843" s="2">
         <v>0</v>
       </c>
       <c r="H1843" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1844" spans="1:8" x14ac:dyDescent="0.25">
@@ -63558,13 +63558,13 @@
         <v>42</v>
       </c>
       <c r="F1846" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1846" s="2">
         <v>0</v>
       </c>
       <c r="H1846" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1847" spans="1:8" x14ac:dyDescent="0.25">
@@ -75960,13 +75960,13 @@
         <v>4047</v>
       </c>
       <c r="F2323" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2323" s="2">
         <v>1</v>
       </c>
       <c r="H2323" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2324" spans="1:8" x14ac:dyDescent="0.25">
@@ -86098,13 +86098,13 @@
         <v>637</v>
       </c>
       <c r="F2713" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2713" s="2">
         <v>0</v>
       </c>
       <c r="H2713" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2714" spans="1:8" x14ac:dyDescent="0.25">
@@ -89348,13 +89348,13 @@
         <v>65</v>
       </c>
       <c r="F2838" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G2838" s="2">
         <v>0</v>
       </c>
       <c r="H2838" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2839" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOCK HARAPAN.xlsx
+++ b/STOK DEALER/STOCK HARAPAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7CD17A-AA54-4E3A-865C-20BC76E763F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361869EA-DC7E-4272-B9ED-DA390AF32F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16512,13 +16512,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17526,13 +17526,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17734,13 +17734,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17864,13 +17864,13 @@
         <v>148</v>
       </c>
       <c r="F88" s="2">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G88" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -18176,13 +18176,13 @@
         <v>98</v>
       </c>
       <c r="F100" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G100" s="2">
         <v>2</v>
       </c>
       <c r="H100" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18202,13 +18202,13 @@
         <v>148</v>
       </c>
       <c r="F101" s="2">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="G101" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H101" s="2">
-        <v>658</v>
+        <v>644</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -18384,13 +18384,13 @@
         <v>148</v>
       </c>
       <c r="F108" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G108" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H108" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28260,13 +28260,13 @@
         <v>363</v>
       </c>
       <c r="F488" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G488" s="2">
         <v>0</v>
       </c>
       <c r="H488" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
@@ -28908,13 +28908,13 @@
         <v>127</v>
       </c>
       <c r="F513" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G513" s="2">
         <v>0</v>
       </c>
       <c r="H513" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
@@ -33012,13 +33012,13 @@
         <v>854</v>
       </c>
       <c r="F671" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G671" s="2">
         <v>0</v>
       </c>
       <c r="H671" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
@@ -34572,13 +34572,13 @@
         <v>42</v>
       </c>
       <c r="F731" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G731" s="2">
         <v>0</v>
       </c>
       <c r="H731" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
@@ -35092,13 +35092,13 @@
         <v>428</v>
       </c>
       <c r="F751" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G751" s="2">
         <v>0</v>
       </c>
       <c r="H751" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
@@ -39333,10 +39333,10 @@
         <v>2</v>
       </c>
       <c r="G914" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H914" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
@@ -39928,13 +39928,13 @@
         <v>1556</v>
       </c>
       <c r="F937" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G937" s="2">
         <v>0</v>
       </c>
       <c r="H937" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
@@ -49157,10 +49157,10 @@
         <v>3</v>
       </c>
       <c r="G1292" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1292" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
@@ -75960,13 +75960,13 @@
         <v>4047</v>
       </c>
       <c r="F2323" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G2323" s="2">
         <v>1</v>
       </c>
       <c r="H2323" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2324" spans="1:8" x14ac:dyDescent="0.25">
@@ -85269,10 +85269,10 @@
         <v>13</v>
       </c>
       <c r="G2681" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2681" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2682" spans="1:8" x14ac:dyDescent="0.25">
@@ -86020,13 +86020,13 @@
         <v>65</v>
       </c>
       <c r="F2710" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G2710" s="2">
         <v>0</v>
       </c>
       <c r="H2710" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2711" spans="1:8" x14ac:dyDescent="0.25">
@@ -89351,10 +89351,10 @@
         <v>12</v>
       </c>
       <c r="G2838" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2838" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2839" spans="1:8" x14ac:dyDescent="0.25">
